--- a/data/pack/ca/canola_elevador.xlsx
+++ b/data/pack/ca/canola_elevador.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5439,6 +5439,61 @@
         </is>
       </c>
       <c r="K91" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>canola_elevador</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Canola, oferta de elevador (Alberta)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>754.4400000000001</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5542,7 +5597,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5608,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -5648,7 +5703,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>

--- a/data/pack/ca/canola_elevador.xlsx
+++ b/data/pack/ca/canola_elevador.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5494,6 +5494,61 @@
         </is>
       </c>
       <c r="K92" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>canola_elevador</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Canola, oferta de elevador (Alberta)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>735.4400000000001</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5597,7 +5652,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5663,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -5703,7 +5758,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/data/pack/ca/canola_elevador.xlsx
+++ b/data/pack/ca/canola_elevador.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5549,6 +5549,61 @@
         </is>
       </c>
       <c r="K93" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>canola_elevador</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Canola, oferta de elevador (Alberta)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>734.63</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5652,7 +5707,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5718,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
@@ -5758,7 +5813,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
